--- a/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:09</t>
+          <t>2026-09-01 03:16:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:10</t>
+          <t>2026-09-01 03:16:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:11</t>
+          <t>2026-09-01 03:16:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:11</t>
+          <t>2026-09-01 03:16:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:11</t>
+          <t>2026-09-01 03:16:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:11</t>
+          <t>2026-09-01 03:16:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:11</t>
+          <t>2026-09-01 03:16:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:11</t>
+          <t>2026-09-01 03:16:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:11</t>
+          <t>2026-09-01 03:16:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:11</t>
+          <t>2026-09-01 03:16:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:11</t>
+          <t>2026-09-01 03:16:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:11</t>
+          <t>2026-09-01 03:16:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">

--- a/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">

--- a/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.93%3425</t>
+          <t>-0.44%3410</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3425</v>
+        <v>3410</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.84%14180</t>
+          <t>-0.21%14150</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>14180</v>
+        <v>14150</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.62%2405</t>
+          <t>+1.46%2440</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2405</v>
+        <v>2440</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+8.28%7650</t>
+          <t>-0.92%7580</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+8.28%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7650</v>
+        <v>7580</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.09%5485</t>
+          <t>+2.83%5640</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5485</v>
+        <v>5640</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.98%2170</t>
+          <t>+6.68%2315</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.98%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2170</v>
+        <v>2315</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-10%999</t>
+          <t>-2.8%971</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>999</v>
+        <v>971</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4.24%2035</t>
+          <t>+8.35%2205</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>+8.35%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2035</v>
+        <v>2205</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-7.11%1175</t>
+          <t>0%1175</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-7.11%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-7.77%629</t>
+          <t>+6.04%667</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-7.77%</t>
+          <t>+6.04%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>629</v>
+        <v>667</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.8%126.5</t>
+          <t>+1.98%129</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>126.5</v>
+        <v>129</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.99%5130</t>
+          <t>+5.46%5410</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>+5.46%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5130</v>
+        <v>5410</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+9.98%242.5</t>
+          <t>-3.3%234.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>242.5</v>
+        <v>234.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+9.91%477</t>
+          <t>+9.85%524</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+9.91%</t>
+          <t>+9.85%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>477</v>
+        <v>524</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:45</t>
+          <t>2026-09-01 15:29:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0%178</t>
+          <t>+2.25%182</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.25%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-4.19%435</t>
+          <t>+3.45%450</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-4.19%</t>
+          <t>+3.45%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.41%6100</t>
+          <t>-1.72%5995</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6100</v>
+        <v>5995</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.25%4075</t>
+          <t>+4.91%4275</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+4.91%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4075</v>
+        <v>4275</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.81%1230</t>
+          <t>-0.41%1225</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.55%1840</t>
+          <t>+1.36%1865</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1840</v>
+        <v>1865</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-8.9%819</t>
+          <t>+6.72%874</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>+6.72%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>819</v>
+        <v>874</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.51%3925</t>
+          <t>+9.94%4315</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3925</v>
+        <v>4315</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.46%7095</t>
+          <t>+9.94%7800</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>7095</v>
+        <v>7800</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+4.06%500</t>
+          <t>+7%535</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+4.06%</t>
+          <t>+7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>500</v>
+        <v>535</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+6.81%3530</t>
+          <t>-2.97%3425</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+6.81%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>3530</v>
+        <v>3425</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-5.84%548</t>
+          <t>+0.36%550</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.84%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-3.94%305</t>
+          <t>-1.48%300.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.94%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>305</v>
+        <v>300.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+3.54%5990</t>
+          <t>-1.75%5885</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+3.54%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5990</v>
+        <v>5885</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+3.52%999</t>
+          <t>+1.1%1010</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+3.52%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:46</t>
+          <t>2026-09-01 15:29:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0%742</t>
+          <t>-1.48%731</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:47</t>
+          <t>2026-09-01 15:29:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-2.58%755</t>
+          <t>+1.99%770</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:47</t>
+          <t>2026-09-01 15:29:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+2.58%358</t>
+          <t>+0.28%359</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:47</t>
+          <t>2026-09-01 15:29:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.47%1345</t>
+          <t>+2.23%1375</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+2.23%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1345</v>
+        <v>1375</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:47</t>
+          <t>2026-09-01 15:29:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+2.78%16065</t>
+          <t>+6.57%17120</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>+6.57%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>16065</v>
+        <v>17120</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:47</t>
+          <t>2026-09-01 15:29:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.55%89.1</t>
+          <t>+4.6%93.2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.55%</t>
+          <t>+4.6%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>89.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:47</t>
+          <t>2026-09-01 15:29:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.4%1060</t>
+          <t>+3.77%1100</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+3.77%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1060</v>
+        <v>1100</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:47</t>
+          <t>2026-09-01 15:29:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-3.69%1435</t>
+          <t>+1.05%1450</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.69%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1435</v>
+        <v>1450</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:47</t>
+          <t>2026-09-01 15:29:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.49%1960</t>
+          <t>+3.57%2030</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+3.57%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1960</v>
+        <v>2030</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:47</t>
+          <t>2026-09-01 15:29:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.36%1450</t>
+          <t>0%1450</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.36%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:47</t>
+          <t>2026-09-01 15:29:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.98%151.5</t>
+          <t>+1.32%153.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>151.5</v>
+        <v>153.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">

--- a/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:15</t>
+          <t>2026-09-01 15:57:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:16</t>
+          <t>2026-09-01 15:57:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:18</t>
+          <t>2026-09-01 15:57:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:18</t>
+          <t>2026-09-01 15:57:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:18</t>
+          <t>2026-09-01 15:57:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:18</t>
+          <t>2026-09-01 15:57:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:18</t>
+          <t>2026-09-01 15:57:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:18</t>
+          <t>2026-09-01 15:57:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:18</t>
+          <t>2026-09-01 15:57:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:18</t>
+          <t>2026-09-01 15:57:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:18</t>
+          <t>2026-09-01 15:57:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:18</t>
+          <t>2026-09-01 15:57:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">

--- a/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:00</t>
+          <t>2026-09-01 16:16:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:02</t>
+          <t>2026-09-01 16:16:26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:03</t>
+          <t>2026-09-01 16:16:27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:03</t>
+          <t>2026-09-01 16:16:27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:03</t>
+          <t>2026-09-01 16:16:27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:03</t>
+          <t>2026-09-01 16:16:27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:03</t>
+          <t>2026-09-01 16:16:27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:03</t>
+          <t>2026-09-01 16:16:27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:03</t>
+          <t>2026-09-01 16:16:27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:03</t>
+          <t>2026-09-01 16:16:27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:03</t>
+          <t>2026-09-01 16:16:27</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:03</t>
+          <t>2026-09-01 16:16:27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">

--- a/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.01%1,001,000</t>
+          <t>7.82%1,001,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.01%</t>
+          <t>7.82%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.79%235,000</t>
+          <t>7.62%235,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.79%</t>
+          <t>7.62%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.27%1,116,000</t>
+          <t>6.24%1,116,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.92%7580</t>
+          <t>+6.68%2315</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7580</v>
+        <v>2315</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.13%343,000</t>
+          <t>6.16%1,161,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>343000</v>
+        <v>1161000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.96%465,000</t>
+          <t>6.01%465,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.96%</t>
+          <t>6.01%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+6.68%2315</t>
+          <t>-0.92%7580</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+6.68%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2315</v>
+        <v>7580</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.89%1,161,000</t>
+          <t>5.96%343,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.89%</t>
+          <t>5.96%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1161000</v>
+        <v>343000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.79%2,482,000</t>
+          <t>5.52%2,482,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.79%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.11%1,074,000</t>
+          <t>5.43%1,074,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.11%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.48%1,630,000</t>
+          <t>4.39%1,630,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>4.39%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.28%2,231,000</t>
+          <t>3.41%2,231,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.41%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1815富喬</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.98%129</t>
+          <t>+5.46%5410</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.98%</t>
+          <t>+5.46%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>129</v>
+        <v>5410</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.22%10,877,000</t>
+          <t>3.32%268,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>10877000</v>
+        <v>268000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+5.46%5410</t>
+          <t>+9.85%524</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+5.46%</t>
+          <t>+9.85%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5410</v>
+        <v>524</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.21%268,000</t>
+          <t>3.31%2,753,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>268000</v>
+        <v>2753000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>1815富喬</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-3.3%234.5</t>
+          <t>+1.98%129</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>234.5</v>
+        <v>129</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.09%5,445,000</t>
+          <t>3.21%10,877,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>5445000</v>
+        <v>10877000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+9.85%524</t>
+          <t>+2.25%182</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>+2.25%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>524</v>
+        <v>182</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.07%2,753,000</t>
+          <t>3.02%7,245,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2753000</v>
+        <v>7245000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:24</t>
+          <t>2026-09-01 17:54:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+2.25%182</t>
+          <t>-3.3%234.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+2.25%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>182</v>
+        <v>234.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.01%7,245,000</t>
+          <t>2.93%5,445,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.93%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>7245000</v>
+        <v>5445000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.73%2,682,000</t>
+          <t>2.77%2,682,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.72%5995</t>
+          <t>-0.41%1225</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5995</v>
+        <v>1225</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.34%164,000</t>
+          <t>2.72%968,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>164000</v>
+        <v>968000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+4.91%4275</t>
+          <t>-1.72%5995</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+4.91%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4275</v>
+        <v>5995</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.05%215,000</t>
+          <t>2.25%164,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>215000</v>
+        <v>164000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.41%1225</t>
+          <t>+4.91%4275</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+4.91%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1225</v>
+        <v>4275</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.84%639,000</t>
+          <t>2.11%215,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>639000</v>
+        <v>215000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.36%1865</t>
+          <t>+6.72%874</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>+6.72%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1865</v>
+        <v>874</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.64%382,000</t>
+          <t>1.69%844,013</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>382000</v>
+        <v>844013</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+6.72%874</t>
+          <t>+1.36%1865</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+6.72%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>874</v>
+        <v>1865</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.62%844,013</t>
+          <t>1.63%382,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>844013</v>
+        <v>382000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.33%145,000</t>
+          <t>1.43%145,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.28%77,000</t>
+          <t>1.38%77,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.17%1,000,000</t>
+          <t>1.23%1,000,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.52%63,000</t>
+          <t>0.49%63,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.48%373,000</t>
+          <t>0.47%373,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.47%659,000</t>
+          <t>0.45%659,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.75%5885</t>
+          <t>+1.1%1010</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5885</v>
+        <v>1010</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.46%33,000</t>
+          <t>0.45%196,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>33000</v>
+        <v>196000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+1.1%1010</t>
+          <t>-1.75%5885</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1010</v>
+        <v>5885</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.46%196,000</t>
+          <t>0.44%33,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>196000</v>
+        <v>33000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:26</t>
+          <t>2026-09-01 17:54:12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.48%731</t>
+          <t>+1.99%770</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>731</v>
+        <v>770</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.45%261,000</t>
+          <t>0.44%250,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>261000</v>
+        <v>250000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:27</t>
+          <t>2026-09-01 17:54:13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.99%770</t>
+          <t>-1.48%731</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>770</v>
+        <v>731</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.44%250,000</t>
+          <t>0.44%261,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>250000</v>
+        <v>261000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:27</t>
+          <t>2026-09-01 17:54:13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.28%359</t>
+          <t>+6.57%17120</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+6.57%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>359</v>
+        <v>17120</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.42%508,000</t>
+          <t>0.43%11,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>508000</v>
+        <v>11000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:27</t>
+          <t>2026-09-01 17:54:13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:27</t>
+          <t>2026-09-01 17:54:13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+6.57%17120</t>
+          <t>+4.6%93.2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+6.57%</t>
+          <t>+4.6%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>17120</v>
+        <v>93.2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.41%11,000</t>
+          <t>0.42%1,957,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>11000</v>
+        <v>1957000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:27</t>
+          <t>2026-09-01 17:54:13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+4.6%93.2</t>
+          <t>+0.28%359</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+4.6%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>93.2</v>
+        <v>359</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.41%1,957,000</t>
+          <t>0.42%508,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1957000</v>
+        <v>508000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:27</t>
+          <t>2026-09-01 17:54:13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.38%155,000</t>
+          <t>0.39%155,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:27</t>
+          <t>2026-09-01 17:54:13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:27</t>
+          <t>2026-09-01 17:54:13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:27</t>
+          <t>2026-09-01 17:54:13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.34%99,952</t>
+          <t>0.33%99,952</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 16:16:27</t>
+          <t>2026-09-01 17:54:13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">

--- a/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:11</t>
+          <t>2026-09-01 19:37:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:12</t>
+          <t>2026-09-01 19:37:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:13</t>
+          <t>2026-09-01 19:37:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:13</t>
+          <t>2026-09-01 19:37:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:13</t>
+          <t>2026-09-01 19:37:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:13</t>
+          <t>2026-09-01 19:37:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:13</t>
+          <t>2026-09-01 19:37:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:13</t>
+          <t>2026-09-01 19:37:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:13</t>
+          <t>2026-09-01 19:37:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:13</t>
+          <t>2026-09-01 19:37:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:13</t>
+          <t>2026-09-01 19:37:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:13</t>
+          <t>2026-09-01 19:37:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">

--- a/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:03</t>
+          <t>2026-09-01 20:35:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:04</t>
+          <t>2026-09-01 20:35:44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:05</t>
+          <t>2026-09-01 20:35:46</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:05</t>
+          <t>2026-09-01 20:35:46</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:05</t>
+          <t>2026-09-01 20:35:46</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:05</t>
+          <t>2026-09-01 20:35:46</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:05</t>
+          <t>2026-09-01 20:35:46</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:05</t>
+          <t>2026-09-01 20:35:46</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:05</t>
+          <t>2026-09-01 20:35:46</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:05</t>
+          <t>2026-09-01 20:35:46</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:05</t>
+          <t>2026-09-01 20:35:46</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 19:37:05</t>
+          <t>2026-09-01 20:35:46</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
